--- a/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1055,11 +1000,6 @@
       </c>
       <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Mantenimiento/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>003 LOS PASTORCITOS DE LA VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.7642</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.8279</v>
-      </c>
-      <c r="I2" t="n">
-        <v>386</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.7642</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.8279</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>386</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>10003</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.76731</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.83222000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>814</v>
-      </c>
-      <c r="J3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.76731</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.83222</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>10024 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.777221</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.84842999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>760</v>
-      </c>
-      <c r="J4" t="n">
-        <v>38</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.777221</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.84843</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>11006 RAMON ESPINOZA SIERRA / RAMON ESPINOZA SIERRA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.76582</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.84587000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>758</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.76582</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.84587</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>11016 JUAN MEJIA BACA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.77697</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.8476</v>
-      </c>
-      <c r="I6" t="n">
-        <v>420</v>
-      </c>
-      <c r="J6" t="n">
-        <v>28</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.77697</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.8476</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>PEDRO ABEL LABARTHE DURAND</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.77495</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.84011</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1440</v>
-      </c>
-      <c r="J7" t="n">
-        <v>96</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.77495</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.84011</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>SANTA LUCIA SCHOOL</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.77243</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.86939</v>
-      </c>
-      <c r="I8" t="n">
-        <v>162</v>
-      </c>
-      <c r="J8" t="n">
-        <v>21</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.77243</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.86939</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>COAR LAMBAYEQUE</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.776861</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.847033</v>
-      </c>
-      <c r="I9" t="n">
-        <v>292</v>
-      </c>
-      <c r="J9" t="n">
-        <v>32</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.776861</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.847033</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>030 VICTORIA SILVA DE DALL'ORSO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.77464</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.84671</v>
-      </c>
-      <c r="I10" t="n">
-        <v>467</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.77464</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.84671</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>10004</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.76829</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.83018</v>
-      </c>
-      <c r="I11" t="n">
-        <v>714</v>
-      </c>
-      <c r="J11" t="n">
-        <v>30</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.76829</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.83018</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>OLIVOS</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.78807</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.87043</v>
-      </c>
-      <c r="I12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.78807</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.87043</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
   </sheetData>
